--- a/data/processed/positivacao/2026-02_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2026-02_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26583,7 +26583,7 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr"/>
@@ -37649,7 +37649,7 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr"/>
@@ -66047,7 +66047,7 @@
     <row r="2529">
       <c r="A2529" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2529" t="inlineStr"/>
@@ -67666,12 +67666,12 @@
       <c r="A2592" t="inlineStr"/>
       <c r="B2592" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 2 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 3.991,07
+          <t>Vendedor 1 - VENDEDOR 01: positivou 2 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 3.991,07
 Vendedor 18 - LOJA: positivou 266 cliente(s), não positivou 649 cliente(s) - Total vendido: R$ 76.486,86
-Vendedor 3 - FERNANDA: positivou 106 cliente(s), não positivou 319 cliente(s) - Total vendido: R$ 135.201,61
-Vendedor 4 - DANIELA: positivou 121 cliente(s), não positivou 523 cliente(s) - Total vendido: R$ 65.966,67
+Vendedor 3 - VENDEDOR 03: positivou 106 cliente(s), não positivou 319 cliente(s) - Total vendido: R$ 135.201,61
+Vendedor 4 - VENDEDOR 04: positivou 121 cliente(s), não positivou 523 cliente(s) - Total vendido: R$ 65.966,67
 Vendedor 5 - SITE: positivou 3 cliente(s), não positivou 444 cliente(s) - Total vendido: R$ 279,35
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2592" t="inlineStr"/>
